--- a/_dossiers/02_Dossier_ADVENIR/02_Tableau_20_PDC.xlsx
+++ b/_dossiers/02_Dossier_ADVENIR/02_Tableau_20_PDC.xlsx
@@ -115,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -135,11 +135,39 @@
       <top style="medium"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -203,6 +231,8 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -568,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -751,7 +781,7 @@
         <v>1860</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
@@ -879,7 +909,7 @@
         <v>1860</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
@@ -1007,7 +1037,7 @@
         <v>1860</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
@@ -1135,7 +1165,7 @@
         <v>1860</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1293,7 @@
         <v>1860</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
@@ -1391,7 +1421,7 @@
         <v>1860</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
@@ -1519,7 +1549,7 @@
         <v>1860</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
@@ -1647,7 +1677,7 @@
         <v>1860</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
@@ -1775,7 +1805,7 @@
         <v>1860</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
@@ -1903,7 +1933,7 @@
         <v>1860</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
@@ -1970,7 +2000,10 @@
         <v>1860</v>
       </c>
       <c r="N24" s="14" t="n"/>
-      <c r="O24" s="12" t="inlineStr"/>
+      <c r="O24" s="12">
+        <f> 75.2 % du HT materiel</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -1978,6 +2011,13 @@
           <t>TOTAUX — 10 stations  |  20 PDC  |  440 kW  |  37 200 EUR ADVENIR</t>
         </is>
       </c>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="24" t="n"/>
       <c r="I25" s="16">
         <f>SUM(I5:I24)</f>
         <v/>
@@ -2083,7 +2123,7 @@
         <v>7440</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>11604</v>
+        <v>9896</v>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
@@ -2115,7 +2155,7 @@
         <v>3720</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -2147,7 +2187,7 @@
         <v>3720</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
@@ -2179,7 +2219,7 @@
         <v>3720</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -2211,7 +2251,7 @@
         <v>3720</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
@@ -2243,7 +2283,7 @@
         <v>7440</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>11604</v>
+        <v>9896</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -2275,7 +2315,7 @@
         <v>3720</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5802</v>
+        <v>4948</v>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
@@ -2346,7 +2386,7 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>- e-Premium AC 2x22 kW : 5 802 EUR HT/borne (devis E-TOTEM ref. DEV17000172-6)</t>
+          <t>- e-Premium AC 2x22 kW : 4948 EUR HT/borne (devis E-TOTEM ref. DEV26000037 du 30/04/2026)</t>
         </is>
       </c>
     </row>
@@ -2367,10 +2407,12 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Taux de couverture ADVENIR : 37 200 EUR / 58 020 EUR HT = 64,1% (exceptionnel en DROM)</t>
-        </is>
-      </c>
-    </row>
+          <t>- Taux de couverture ADVENIR : 37 200 EUR / 49 480 EUR HT = 75.2% (exceptionnel en DROM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A43:O43"/>
